--- a/processed_ruby_restored_xlsx/sc214_ノノ６：水泳特訓.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc214_ノノ６：水泳特訓.ss.xlsx
@@ -560,8 +560,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Peeking shyly in through the open door was, of course,
-Nono-chan.</t>
+          <t>Peeking shyly in through the open door was, of
+course, Nono-chan.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -712,8 +712,8 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan was as polite as always, but her face lacked
-its usual energy.</t>
+          <t>Nono-chan was as polite as always, but her face
+lacked its usual energy.</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1183,8 +1183,8 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>I see — that getup was precisely because they couldn’t
-swim.</t>
+          <t>I see — that getup was precisely because they
+couldn’t swim.</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1951,7 +1951,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Uh... no, it's just—what's up with that swimsuit...？」</t>
+          <t>「Uh... no, it's just—what's up with that
+swimsuit...？」</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2028,8 +2029,8 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>I never thought I'd get to see this nostalgic swimsuit
-with my own eyes again.</t>
+          <t>I never thought I'd get to see this nostalgic
+swimsuit with my own eyes again.</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2595,8 +2596,8 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>The sleek design only makes Nono-chan's beautiful body
-stand out more.</t>
+          <t>The sleek design only makes Nono-chan's beautiful
+body stand out more.</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2626,8 +2627,8 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>If that spot opens and a bit of bare skin peeks out, I
-think I couldn't handle it...！</t>
+          <t>If that spot opens and a bit of bare skin peeks out,
+I think I couldn't handle it...！</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2702,8 +2703,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>I was so absorbed in her swimsuit that I didn't notice
-her face had come close.</t>
+          <t>I was so absorbed in her swimsuit that I didn't
+notice her face had come close.</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2991,8 +2992,8 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, she once hid her embarrassment by
-diving underwater.</t>
+          <t>Come to think of it, she once hid her embarrassment
+by diving underwater.</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3100,8 +3101,8 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>「...Your knees are bent, so keep them straight and try
-flapping them, okay？」</t>
+          <t>「...Your knees are bent, so keep them straight and
+try flapping them, okay？」</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3176,8 +3177,9 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>「You don't have to kick the water so hard. Think about
-moving forward… but you can be more relaxed about it.」</t>
+          <t>「You don't have to kick the water so hard. Think
+about moving forward… but you can be more relaxed
+about it.」</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3252,8 +3254,8 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan picks things up fast, so she learns whatever
-I teach her right away.</t>
+          <t>Nono-chan picks things up fast, so she learns
+whatever I teach her right away.</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3494,7 +3496,8 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>The more she did it, the more the shape of her butt...</t>
+          <t>The more she did it, the more the shape of her
+butt...</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3907,8 +3910,8 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>If we actually went to the pool, what if she just sank
-like that...</t>
+          <t>If we actually went to the pool, what if she just
+sank like that...</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -4000,8 +4003,8 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>I can picture everyone seeing the kickboard and going,
-『Oh ho~,』 but…</t>
+          <t>I can picture everyone seeing the kickboard and
+going, 『Oh ho~,』 but…</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4106,8 +4109,8 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>「What do you mean—stretching…！ After swimming you have
-to loosen your body up…！」</t>
+          <t>「What do you mean—stretching…！ After swimming you
+have to loosen your body up…！」</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4396,8 +4399,8 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>I laid Nono‑chan down on the beach and lifted her legs
-high.</t>
+          <t>I laid Nono‑chan down on the beach and lifted her
+legs high.</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4457,7 +4460,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>「This will... really help loosen your body, you know？」</t>
+          <t>「This will... really help loosen your body, you
+know？」</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4503,7 +4507,8 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>「W-wait, um...！ Why are you taking my clothes off...？」</t>
+          <t>「W-wait, um...！ Why are you taking my clothes
+off...？」</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4686,8 +4691,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Her thin, delicate legs were surprisingly well-padded,
-plump and really pleasant to the touch.</t>
+          <t>Her thin, delicate legs were surprisingly
+well-padded, plump and really pleasant to the touch.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4748,8 +4753,8 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Mm, it's a massage... you've been doing flutter kicks
-hard, so I'll soften you up.」</t>
+          <t>「Mm, it's a massage... you've been doing flutter
+kicks hard, so I'll soften you up.」</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -5178,7 +5183,8 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan says she cares, but her body says otherwise.</t>
+          <t>Nono-chan says she cares, but her body says
+otherwise.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5239,7 +5245,8 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, calming her breath, entrusts herself to me.</t>
+          <t>Nono-chan, calming her breath, entrusts herself to
+me.</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5301,7 +5308,8 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Hah... ah, nngh！ I feel my strength slipping away...」</t>
+          <t>「Hah... ah, nngh！ I feel my strength slipping
+away...」</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5792,8 +5800,8 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>Being shown Nono-chan's adorable appearance like this,
-there's no way I wouldn't be turned on.</t>
+          <t>Being shown Nono-chan's adorable appearance like
+this, there's no way I wouldn't be turned on.</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -6130,8 +6138,8 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>The wetness my glans felt inside her pussy was clearly
-more than just water.</t>
+          <t>The wetness my glans felt inside her pussy was
+clearly more than just water.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6146,8 +6154,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Seeing Nono-chan's body coming together like that made
-it impossible to hold back any longer.</t>
+          <t>Seeing Nono-chan's body coming together like that
+made it impossible to hold back any longer.</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6222,7 +6230,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>She was totally full, but Nono-chan nodded obediently.</t>
+          <t>She was totally full, but Nono-chan nodded
+obediently.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6574,8 +6583,8 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t>Earlier I had been using my hand, but now I licked and
-massaged with my tongue.</t>
+          <t>Earlier I had been using my hand, but now I licked
+and massaged with my tongue.</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6590,8 +6599,8 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>At the same time I rocked my hips to help her get used
-to the penis.</t>
+          <t>At the same time I rocked my hips to help her get
+used to the penis.</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6621,7 +6630,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>「U, ha！ Haa, haa... phew... nn！ Nn... fuuh！ Fuhaa...！」</t>
+          <t>「U, ha！ Haa, haa... phew... nn！ Nn... fuuh！
+Fuhaa...！」</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -7200,8 +7210,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>But there was a look of expectation in those eyes that
-made my heart skip a beat.</t>
+          <t>But there was a look of expectation in those eyes
+that made my heart skip a beat.</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7551,8 +7561,8 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>When I lifted the fabric between her legs, Nono-chan's
-breathing changed.</t>
+          <t>When I lifted the fabric between her legs,
+Nono-chan's breathing changed.</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7642,8 +7652,8 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>「Eh？ Ah, no！ If that's the case, ah, you'll be able to
-see down there...！」</t>
+          <t>「Eh？ Ah, no！ If that's the case, ah, you'll be able
+to see down there...！」</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7779,9 +7789,9 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>Slowly, making me aware of the presence of my penis as
-she pulled her hips back, her pussy clenched tight as
-if it didn’t want to let go.</t>
+          <t>Slowly, making me aware of the presence of my penis
+as she pulled her hips back, her pussy clenched tight
+as if it didn’t want to let go.</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7796,8 +7806,8 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>So, pressing my hips down with a long, heavy thrust, I
-slowly push my penis in again.</t>
+          <t>So, pressing my hips down with a long, heavy thrust,
+I slowly push my penis in again.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7843,8 +7853,8 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>What she was shy about earlier, she's saying naturally
-now.</t>
+          <t>What she was shy about earlier, she's saying
+naturally now.</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7935,7 +7945,8 @@
       <c r="B489" s="1" t="inlineStr">
         <is>
           <t>I thrust in a little harder without thinking, and she
-let out an even higher cry as her tiny body went limp.</t>
+let out an even higher cry as her tiny body went
+limp.</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -8253,8 +8264,8 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, I wonder... you'll have to do more... mmmph！ I-I
-don't know...」</t>
+          <t>「Mmm, I wonder... you'll have to do more... mmmph！
+I-I don't know...」</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8299,8 +8310,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>Hearing Nono-chan's clumsy begging makes me unbearably
-fond of her.</t>
+          <t>Hearing Nono-chan's clumsy begging makes me
+unbearably fond of her.</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8825,8 +8836,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>Also, I want to properly let her know that I'm feeling
-it too.</t>
+          <t>Also, I want to properly let her know that I'm
+feeling it too.</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8979,8 +8990,8 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Penis… ah！？ It twitched again… nnnhhh！ I… I can
-feel it…！」</t>
+          <t>「Nnnh！ Penis… ah！？ It twitched again… nnnhhh！ I… I
+can feel it…！」</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9026,8 +9037,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>When words and feelings start to overlap, the pleasure
-just keeps welling up stronger and stronger.</t>
+          <t>When words and feelings start to overlap, the
+pleasure just keeps welling up stronger and stronger.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9118,8 +9129,8 @@
       </c>
       <c r="B566" s="1" t="inlineStr">
         <is>
-          <t>Wanting to feel Nono-chan even more deeply, I drove my
-penis all the way in.</t>
+          <t>Wanting to feel Nono-chan even more deeply, I drove
+my penis all the way in.</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -9212,8 +9223,8 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>She bounced her hips, her body twitching and writhing,
-but she moved with me.</t>
+          <t>She bounced her hips, her body twitching and
+writhing, but she moved with me.</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -9320,8 +9331,8 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haa... yes！ It feels... good, nuahh！ It feels...
-good...」</t>
+          <t>「Hah, haa... yes！ It feels... good, nuahh！ It
+feels... good...」</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -9476,8 +9487,8 @@
       </c>
       <c r="B589" s="1" t="inlineStr">
         <is>
-          <t>I wanted to come, wanted it so bad that it screamed up
-from deep inside me！</t>
+          <t>I wanted to come, wanted it so bad that it screamed
+up from deep inside me！</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9568,8 +9579,8 @@
       </c>
       <c r="B595" s="1" t="inlineStr">
         <is>
-          <t>「Inside... ah, inside Nono-chan... I'm going to put it
-all out... I'm going to cum inside, okay！？」</t>
+          <t>「Inside... ah, inside Nono-chan... I'm going to put
+it all out... I'm going to cum inside, okay！？」</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -9966,7 +9977,8 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Nn-ah！ Ha, y-yes！ Mui-sensei...！ Nn！ Nn！ Nngkuuu...！」</t>
+          <t>「Nn-ah！ Ha, y-yes！ Mui-sensei...！ Nn！ Nn！
+Nngkuuu...！」</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10924,8 +10936,8 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>Under the hot summer sun, our flushed bodies burn even
-hotter...</t>
+          <t>Under the hot summer sun, our flushed bodies burn
+even hotter...</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -10972,8 +10984,8 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>After fetching it and taking off my shoes at the front
-door, Nono-chan happened to be passing by.</t>
+          <t>After fetching it and taking off my shoes at the
+front door, Nono-chan happened to be passing by.</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -11170,8 +11182,8 @@
       </c>
       <c r="B700" s="1" t="inlineStr">
         <is>
-          <t>When I held out the box, Nono-chan took it eagerly and
-immediately started opening it.</t>
+          <t>When I held out the box, Nono-chan took it eagerly
+and immediately started opening it.</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -11342,8 +11354,8 @@
       </c>
       <c r="B711" s="1" t="inlineStr">
         <is>
-          <t>Quick to understand, Nono-chan is already horrified at
-what the future might hold.</t>
+          <t>Quick to understand, Nono-chan is already horrified
+at what the future might hold.</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11373,8 +11385,8 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... last time we could only do the legs... but if
-you use this you can actually swim in the pool！」</t>
+          <t>「Yeah... last time we could only do the legs... but
+if you use this you can actually swim in the pool！」</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -11451,8 +11463,8 @@
       </c>
       <c r="B718" s="1" t="inlineStr">
         <is>
-          <t>「B-but wanting to be able to swim in the sea is asking
-too much...」</t>
+          <t>「B-but wanting to be able to swim in the sea is
+asking too much...」</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -11620,8 +11632,8 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>When I gave in and said that, Nono-chan responded with
-determined energy.</t>
+          <t>When I gave in and said that, Nono-chan responded
+with determined energy.</t>
         </is>
       </c>
       <c r="C729" t="n">

--- a/processed_ruby_restored_xlsx/sc214_ノノ６：水泳特訓.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc214_ノノ６：水泳特訓.ss.xlsx
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>「So！ I'm sure this swimsuit's happy about it too！」</t>
+          <t>So！ I'm sure this swimsuit's happy about it too！</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>「Hehe... yeah...」</t>
+          <t>Hehe... yeah...</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>「Hah… y-yes！ Nngh… nnghh~！」</t>
+          <t>Hah… y-yes！ Nngh… nnghh~！</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3497,7 +3497,7 @@
       <c r="B199" s="1" t="inlineStr">
         <is>
           <t>The more she did it, the more the shape of her
-butt...</t>
+butt..."</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3603,7 +3603,7 @@
       <c r="B206" s="1" t="inlineStr">
         <is>
           <t>She made my heart race in little moments like that,
-but she still kept seriously training...！</t>
+but she still kept seriously training...！"</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3740,8 +3740,8 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>「No, no！ That's because Janitor-sensei was so good at
-teaching！」</t>
+          <t>No, no！ That's because Janitor-sensei was so good at
+teaching！</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3911,7 +3911,7 @@
       <c r="B226" s="1" t="inlineStr">
         <is>
           <t>If we actually went to the pool, what if she just
-sank like that...</t>
+sank like that..."</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>「Hmm？ Janitor-sensei, what's the matter？」</t>
+          <t>Hmm？ Janitor-sensei, what's the matter？</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>「Y- Janitor-sensei... th-this is...」</t>
+          <t>Y- Janitor-sensei... th-this is...</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4476,8 +4476,8 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I even slipped down her shoulder straps,
-exposing her cute little chest.</t>
+          <t>Saying that, he even slipped down her shoulder
+straps, exposing her cute little chest.</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>First, I began to knead her taut, outstretched legs.</t>
+          <t>First, he began to knead her taut, outstretched legs.</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Pressing my fingers in, I continued the thorough
+          <t>Pressing his fingers in, he continued the thorough
 massage.</t>
         </is>
       </c>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>Using a flimsy excuse, this time I reach for the
+          <t>Using a flimsy excuse, this time he reaches for the
 swimsuit that made me horny.</t>
         </is>
       </c>
@@ -5261,8 +5261,9 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>Taking advantage of that, this time I traced around
-the base of the thigh with a finger and slid upward.</t>
+          <t>Taking advantage of that, this time they traced
+around the base of the thigh with a finger and slid
+upward.</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5491,7 +5492,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>「Eah！？ Nn... nnh... Janitor-sensei...」</t>
+          <t>Eah！？ Nn... nnh... Janitor-sensei...</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5506,7 +5507,7 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>When I stroked every reachable place, Nono-chan,
+          <t>When he stroked every reachable place, Nono-chan,
 confused, sent a wistful look out over the waves.</t>
         </is>
       </c>
@@ -5615,8 +5616,8 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>「Th-that... um... because Janitor-sensei is touching
-me, after all...」</t>
+          <t>Th-that... um... because Janitor-sensei is touching
+me, after all...</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -5723,8 +5724,8 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t>She doesn't seem to be objecting or refusing, but she
-isn't making any big movements.</t>
+          <t>They don't seem to be objecting or refusing, but they
+aren't making any big movements.</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -6382,8 +6383,8 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>「Ha... ah！ Janitor-sensei, you're doing it too...！
-It's so warm... nn！ Haa...」</t>
+          <t>Ha... ah！ Janitor-sensei, you're doing it too...！
+It's so warm... nn！ Haa...</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6475,8 +6476,8 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>「I-I can... feel it, uunh！ Janitor-sensei's penis
-is... rubbing inside me...」</t>
+          <t>I-I can... feel it, uunh！ Janitor-sensei's penis
+is... rubbing inside me...</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -7241,7 +7242,7 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nn, fuaaah！？」</t>
+          <t>Nn... nn, fuaaah！？</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -7256,7 +7257,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>Startled, my penis bounced up inside her pussy.</t>
+          <t>Startled, his penis bounced up inside her pussy.</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7286,7 +7287,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Y-You okay？」</t>
+          <t>Ah！ Y-You okay？</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7348,7 +7349,7 @@
       <c r="B450" s="1" t="inlineStr">
         <is>
           <t>The penis wants to move a lot and its pulse quickens,
-but I hold back hard to match Nono-chan's pace.</t>
+but he holds back hard to match Nono-chan's pace.</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -7789,7 +7790,7 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>Slowly, making me aware of the presence of my penis
+          <t>Slowly, making him aware of the presence of his penis
 as she pulled her hips back, her pussy clenched tight
 as if it didn’t want to let go.</t>
         </is>
@@ -7806,8 +7807,8 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>So, pressing my hips down with a long, heavy thrust,
-I slowly push my penis in again.</t>
+          <t>So, pressing his hips down with a long, heavy thrust,
+he slowly pushes his penis in again.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -8836,7 +8837,7 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>Also, I want to properly let her know that I'm
+          <t>Also, I want to properly let them know that I'm
 feeling it too.</t>
         </is>
       </c>
@@ -9160,8 +9161,8 @@
       </c>
       <c r="B568" s="1" t="inlineStr">
         <is>
-          <t>「Ah, wow...！ Ah！ It's... Mui-sensei's penis...！ It's
-all slippery... haaah！」</t>
+          <t>Ah, wow...！ Ah！ It's... Mui-sensei's penis...！ It's
+all slippery... haaah！</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -9686,7 +9687,7 @@
       </c>
       <c r="B602" s="1" t="inlineStr">
         <is>
-          <t>「Nnhhaaahhhh...！ Ah... aaahh！ Hah！ Haaah！」</t>
+          <t>Nnhhaaahhhh...！ Ah... aaahh！ Hah！ Haaah！</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -9716,7 +9717,7 @@
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
-          <t>「Haa, Nono-chan！ Nono-chaaan！」</t>
+          <t>Haa, Nono-chan！ Nono-chaaan！</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -9731,8 +9732,8 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>I kept thinking about Nono-chan, and with that very
-thought I shot my cum.</t>
+          <t>He kept thinking about Nono-chan, and with that very
+thought he shot his cum.</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -9793,8 +9794,8 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>「Huh！ Fwaaah... heh, uah... ahh, nnngh... Yomu...
-I-—senseeeer...」</t>
+          <t>Huh！ Fwaaah... heh, uah... ahh, nnngh... Yomu...
+I-—senseeeer...</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9871,7 +9872,7 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>「Aahh, nn... fuyaa, fuu... faaah...」</t>
+          <t>Aahh, nn... fuyaa, fuu... faaah...</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9977,8 +9978,7 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Nn-ah！ Ha, y-yes！ Mui-sensei...！ Nn！ Nn！
-Nngkuuu...！」</t>
+          <t>Nn-ah！ Ha, y-yes！ Mui-sensei...！ Nn！ Nn！ Nngkuuu...！</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>At the moment of climax, my penis slips out from the
+          <t>At the moment of climax, his penis slips out from the
 force of it, but what rises up can't be stopped...</t>
         </is>
       </c>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>「Y-yo, Muiin, sensei... Ah！？ Not yet！？」</t>
+          <t>Y-yo, Muiin, sensei... Ah！？ Not yet！？</t>
         </is>
       </c>
       <c r="C632" t="n">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>「Fuwaa... ahh, nn, mmm...！」</t>
+          <t>Fuwaa... ahh, nn, mmm...！</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... Nono-chan...」</t>
+          <t>Ahh... Nono-chan...</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>Slowly pulling my penis out, thick white semen
+          <t>Slowly pulling his penis out, thick white semen
 trickles out from the gap.</t>
         </is>
       </c>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="B689" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Janitor-sensei！ What's that？」</t>
+          <t>Ah... Janitor-sensei！ What's that？</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>「Heh... so, shall we go right now？」</t>
+          <t>Heh... so, shall we go right now？</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... uuu... Janitor-sensei is such a perv！」</t>
+          <t>Ugh... uuu... Janitor-sensei is such a perv！</t>
         </is>
       </c>
       <c r="C750" t="n">
